--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0007_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0007_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -908,7 +909,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B23" s="0">
         <v>0</v>
@@ -984,7 +985,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B25" s="0">
         <v>0</v>
@@ -1081,7 +1082,7 @@
         <v>0.18105009052504509</v>
       </c>
       <c r="H27" s="0">
-        <v>0.3124467420326078</v>
+        <v>0.31244674203260781</v>
       </c>
       <c r="I27" s="0">
         <v>0.18668944013028524</v>
@@ -1160,7 +1161,7 @@
         <v>1.3293188661023752</v>
       </c>
       <c r="I29" s="0">
-        <v>0.69909237155171033</v>
+        <v>0.69909237155171034</v>
       </c>
       <c r="J29" s="0">
         <v>1.3617960986382103</v>
@@ -1309,13 +1310,13 @@
         <v>4.2043854355260475</v>
       </c>
       <c r="H33" s="0">
-        <v>4.289041640629434</v>
+        <v>4.2890416406294341</v>
       </c>
       <c r="I33" s="0">
         <v>3.517308494369523</v>
       </c>
       <c r="J33" s="0">
-        <v>4.6374677953625278</v>
+        <v>4.6374677953625279</v>
       </c>
       <c r="K33" s="0">
         <v>7.6030927835051472</v>
@@ -1364,7 +1365,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>3.6526533425224152</v>
+        <v>3.6526533425224153</v>
       </c>
       <c r="B35" s="0">
         <v>6.1403508771930104</v>
@@ -1388,10 +1389,10 @@
         <v>4.2663182412089045</v>
       </c>
       <c r="I35" s="0">
-        <v>4.7764691863121111</v>
+        <v>4.7764691863121112</v>
       </c>
       <c r="J35" s="0">
-        <v>4.9135075450865155</v>
+        <v>4.9135075450865156</v>
       </c>
       <c r="K35" s="0">
         <v>11.082474226804175</v>
@@ -1537,7 +1538,7 @@
         <v>3.0175015087507515</v>
       </c>
       <c r="H39" s="0">
-        <v>2.6586377322047356</v>
+        <v>2.6586377322047357</v>
       </c>
       <c r="I39" s="0">
         <v>4.4467835792734958</v>
@@ -1619,7 +1620,7 @@
         <v>3.7496772655955373</v>
       </c>
       <c r="J41" s="0">
-        <v>2.1715126978284975</v>
+        <v>2.1715126978284976</v>
       </c>
       <c r="K41" s="0">
         <v>1.4175257731958828</v>
@@ -1683,7 +1684,7 @@
         <v>3.2602404606342641</v>
       </c>
       <c r="F43" s="0">
-        <v>3.2347269220972938</v>
+        <v>3.2347269220972939</v>
       </c>
       <c r="G43" s="0">
         <v>2.9973848320257468</v>
@@ -1782,7 +1783,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>2.7394900068917964</v>
+        <v>2.7394900068917965</v>
       </c>
       <c r="B46" s="0">
         <v>0.17543859649122792</v>
@@ -1832,7 +1833,7 @@
         <v>3.2649724713293256</v>
       </c>
       <c r="E47" s="0">
-        <v>2.8831409051582821</v>
+        <v>2.8831409051582822</v>
       </c>
       <c r="F47" s="0">
         <v>2.6143434122912468</v>
@@ -1873,7 +1874,7 @@
         <v>2.7244249530117224</v>
       </c>
       <c r="F48" s="0">
-        <v>2.4469672160972213</v>
+        <v>2.4469672160972214</v>
       </c>
       <c r="G48" s="0">
         <v>2.152484409575536</v>
@@ -1996,7 +1997,7 @@
         <v>1.7781060046582953</v>
       </c>
       <c r="I51" s="0">
-        <v>2.0237929733272408</v>
+        <v>2.0237929733272409</v>
       </c>
       <c r="J51" s="0">
         <v>1.5274199484725786</v>
@@ -2016,10 +2017,10 @@
         <v>3.1578947368421026</v>
       </c>
       <c r="C52" s="0">
-        <v>2.1392612130511401</v>
+        <v>2.1392612130511402</v>
       </c>
       <c r="D52" s="0">
-        <v>1.7334647657057662</v>
+        <v>1.7334647657057663</v>
       </c>
       <c r="E52" s="0">
         <v>2.3306184552045086</v>
@@ -2092,7 +2093,7 @@
         <v>3.5964912280701724</v>
       </c>
       <c r="C54" s="0">
-        <v>1.926222752000404</v>
+        <v>1.9262227520004041</v>
       </c>
       <c r="D54" s="0">
         <v>1.8079965378789684</v>
@@ -2136,7 +2137,7 @@
         <v>1.9306133243574621</v>
       </c>
       <c r="E55" s="0">
-        <v>2.1480354425848009</v>
+        <v>2.148035442584801</v>
       </c>
       <c r="F55" s="0">
         <v>1.9230069497507534</v>
@@ -2271,7 +2272,7 @@
         <v>1.0309278350515454</v>
       </c>
       <c r="L58" s="0">
-        <v>1.7696637949802489</v>
+        <v>1.769663794980249</v>
       </c>
     </row>
     <row r="59">
@@ -2320,7 +2321,7 @@
         <v>0.35087719298245584</v>
       </c>
       <c r="C60" s="0">
-        <v>1.4304010956263697</v>
+        <v>1.4304010956263698</v>
       </c>
       <c r="D60" s="0">
         <v>1.1131680811675031</v>
@@ -2390,7 +2391,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.3660529683961788</v>
+        <v>1.3660529683961789</v>
       </c>
       <c r="B62" s="0">
         <v>0</v>
@@ -2461,7 +2462,7 @@
         <v>0.38659793814432958</v>
       </c>
       <c r="L63" s="0">
-        <v>1.3591266755823705</v>
+        <v>1.3591266755823706</v>
       </c>
     </row>
     <row r="64">
@@ -2680,7 +2681,7 @@
         <v>0.8350849287053429</v>
       </c>
       <c r="I69" s="0">
-        <v>0.57198466763322064</v>
+        <v>0.57198466763322065</v>
       </c>
       <c r="J69" s="0">
         <v>0.90172984909827925</v>
@@ -2779,16 +2780,16 @@
         <v>0.61755791983159758</v>
       </c>
       <c r="D72" s="0">
-        <v>0.28610583511648568</v>
+        <v>0.28610583511648569</v>
       </c>
       <c r="E72" s="0">
         <v>0.65992422208299706</v>
       </c>
       <c r="F72" s="0">
-        <v>0.7568314958337875</v>
+        <v>0.75683149583378751</v>
       </c>
       <c r="G72" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H72" s="0">
         <v>0.86917002783616348</v>
@@ -2884,7 +2885,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.58580289455547851</v>
+        <v>0.58580289455547852</v>
       </c>
       <c r="B75" s="0">
         <v>0.70175438596491169</v>
@@ -2905,10 +2906,10 @@
         <v>0.50291691812512529</v>
       </c>
       <c r="H75" s="0">
-        <v>0.60785093449980065</v>
+        <v>0.60785093449980066</v>
       </c>
       <c r="I75" s="0">
-        <v>0.3237274334174095</v>
+        <v>0.32372743341740951</v>
       </c>
       <c r="J75" s="0">
         <v>0.69930069930069871</v>
@@ -2931,7 +2932,7 @@
         <v>0.4438301271890332</v>
       </c>
       <c r="D76" s="0">
-        <v>0.28610583511648568</v>
+        <v>0.28610583511648569</v>
       </c>
       <c r="E76" s="0">
         <v>0.4379605596825677</v>
@@ -3399,7 +3400,7 @@
         <v>0.060350030175015036</v>
       </c>
       <c r="H88" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I88" s="0">
         <v>0.041707215348255215</v>
@@ -3475,7 +3476,7 @@
         <v>0.060350030175015036</v>
       </c>
       <c r="H90" s="0">
-        <v>0.068170198261659889</v>
+        <v>0.06817019826165989</v>
       </c>
       <c r="I90" s="0">
         <v>0.017874520863537947</v>
@@ -3492,7 +3493,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.024613566998129346</v>
+        <v>0.024613566998129347</v>
       </c>
       <c r="B91" s="0">
         <v>0.26315789473684187</v>
@@ -3720,7 +3721,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B97" s="0">
         <v>0</v>
